--- a/backlink-building-data.xlsx
+++ b/backlink-building-data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Haider\Backlink-Building\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CAAAF83B-F307-4D9B-A1B6-08954401AE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2984E2E-554A-44EA-8D55-ADC3914BC53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{C5600408-53AE-44CA-94F4-5B3C15A00001}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{C5600408-53AE-44CA-94F4-5B3C15A00001}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Backlink Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Pages Indexed" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,15 +34,196 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+  <si>
+    <t>Backlink Personal and resumebuilder.pk profile Data.</t>
+  </si>
+  <si>
+    <t>https://resumebuilder.pk</t>
+  </si>
+  <si>
+    <t>Tagline</t>
+  </si>
+  <si>
+    <t>Company Name</t>
+  </si>
+  <si>
+    <t>Free AI Resume Builder &amp; CV Maker</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ResumeBuilder.pk helps students, fresh graduates, and professionals create ATS-friendly resumes, CVs, and cover letters using AI-powered tools. Users can choose modern templates, customize resumes online, and download professional PDFs in minutes.</t>
+  </si>
+  <si>
+    <t>Website</t>
+  </si>
+  <si>
+    <t>ResumeBuilder.pk</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>HR Technology / Career Services / Software</t>
+  </si>
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Resume Builder</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>Career</t>
+  </si>
+  <si>
+    <t>HR Tec</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/ResumeBuilder.pk</t>
+  </si>
+  <si>
+    <t>Total Pages</t>
+  </si>
+  <si>
+    <t>Indexed</t>
+  </si>
+  <si>
+    <t>Not Indexed</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/templates</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/features</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/coverletter</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/contact</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/best-cv-format-for-freshers-in-pakistan-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/how-to-make-ats-friendly-resume-in-pakistan-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/top-resume-mistakes-to-avoid-in-pakistan-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/best-resume-skills-for-jobs-in-pakistan-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/resume-vs-cv-difference-in-pakistan-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/software-engineer-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/accountant-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/teacher-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/sales-executive-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://resumebuilder.pk/</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/cover-letter</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/pricing</t>
+  </si>
+  <si>
+    <t>https://resumebuilder.pk/reviews</t>
+  </si>
+  <si>
+    <t>https://resumebuilder.pk/blog/hr-manager-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/how-to-write-professional-cover-letter-in-pakistan-2026</t>
+  </si>
+  <si>
+    <t>https://resumebuilder.pk/ai-resume-builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request indexing on </t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/ats-keywords-for-resumes</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>https://resumebuilder.pk/cv-maker</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Roboto"/>
     </font>
   </fonts>
   <fills count="2">
@@ -52,7 +234,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,14 +242,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -380,9 +596,359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA396663-3F38-44B4-A3C1-4D236BFAAAC9}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="82.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="11"/>
+      <c r="B10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="11"/>
+      <c r="B12" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A9:A12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" display="https://resumebuilder.pk" xr:uid="{FA717E6B-607D-4B77-884F-A6E0E216801C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50891E8-DCBC-4D2B-8051-6E7893B38F89}">
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" customWidth="1"/>
+    <col min="2" max="2" width="85.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>7</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>11</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>13</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="6"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="6">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="6">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>42</v>
+      </c>
+      <c r="E31" s="6">
+        <v>46201</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B28" r:id="rId1" display="https://www.resumebuilder.pk/ai-resume-builder" xr:uid="{2A31CB2E-E9F6-43C8-9E3D-F82DCCBC06E7}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{12517903-CE33-4219-B72F-52864C17E0BE}"/>
+    <hyperlink ref="B31" r:id="rId3" xr:uid="{DCEC65B5-E9DA-4B67-BBAA-8AE2EDF8CCA2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/backlink-building-data.xlsx
+++ b/backlink-building-data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Haider\Backlink-Building\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Backlink-Building\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2984E2E-554A-44EA-8D55-ADC3914BC53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FD2D1B-20CF-4C0B-BD92-FA4E4FF072AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{C5600408-53AE-44CA-94F4-5B3C15A00001}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{C5600408-53AE-44CA-94F4-5B3C15A00001}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlink Data" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="57">
   <si>
     <t>Backlink Personal and resumebuilder.pk profile Data.</t>
   </si>
@@ -160,29 +160,59 @@
     <t>https://www.resumebuilder.pk/blog/how-to-write-professional-cover-letter-in-pakistan-2026</t>
   </si>
   <si>
-    <t>https://resumebuilder.pk/ai-resume-builder</t>
-  </si>
-  <si>
     <t xml:space="preserve">Request indexing on </t>
   </si>
   <si>
     <t>https://www.resumebuilder.pk/blog/ats-keywords-for-resumes</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>https://resumebuilder.pk/cv-maker</t>
   </si>
   <si>
     <t>https://www.resumebuilder.pk/</t>
+  </si>
+  <si>
+    <t>INDEXED</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/ai-resume-builder</t>
+  </si>
+  <si>
+    <t>INDEXED ALREADY</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/ats-resume-guide</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/bank-job-cv-format-in-pakistan-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/best-skills-for-a-resume-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/customer-service-representative-resume-example-2026</t>
+  </si>
+  <si>
+    <t>Not On Google</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/data-entry-operator-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/graphic-designer-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/how-to-write-a-cover-letter</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/how-to-write-a-professional-summary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,12 +243,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Courier New"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="11"/>
@@ -262,7 +286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -277,7 +301,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -653,7 +676,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -661,19 +684,19 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
+      <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
+      <c r="A11" s="10"/>
       <c r="B11" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
+      <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>15</v>
       </c>
@@ -699,12 +722,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50891E8-DCBC-4D2B-8051-6E7893B38F89}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="85.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="2" max="2" width="93.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -897,58 +920,175 @@
       <c r="B25" s="7"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
+      <c r="B26" s="7" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="9" t="s">
+      <c r="A27">
+        <v>1</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>2</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>4</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>5</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="6"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>6</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="6"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>7</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="6"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>8</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" s="6"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>9</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" s="6"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="1"/>
+      <c r="E36" s="6"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="1"/>
+      <c r="E37" s="6"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="1"/>
+      <c r="E38" s="6"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="1"/>
+      <c r="E39" s="6"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
+      <c r="E40" s="6">
+        <v>46201</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="6">
+      <c r="C41" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="6">
         <v>46201</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="6">
-        <v>46201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="6">
-        <v>46201</v>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B28" r:id="rId1" display="https://www.resumebuilder.pk/ai-resume-builder" xr:uid="{2A31CB2E-E9F6-43C8-9E3D-F82DCCBC06E7}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{12517903-CE33-4219-B72F-52864C17E0BE}"/>
-    <hyperlink ref="B31" r:id="rId3" xr:uid="{DCEC65B5-E9DA-4B67-BBAA-8AE2EDF8CCA2}"/>
+    <hyperlink ref="B31" r:id="rId1" xr:uid="{2A31CB2E-E9F6-43C8-9E3D-F82DCCBC06E7}"/>
+    <hyperlink ref="B28" r:id="rId2" xr:uid="{12517903-CE33-4219-B72F-52864C17E0BE}"/>
+    <hyperlink ref="B41" r:id="rId3" xr:uid="{DCEC65B5-E9DA-4B67-BBAA-8AE2EDF8CCA2}"/>
+    <hyperlink ref="B27" r:id="rId4" xr:uid="{CAEBC9F7-D231-40FE-827A-4CF63BFD1492}"/>
+    <hyperlink ref="B29" r:id="rId5" xr:uid="{ACD87C68-3669-4537-AB77-7A72908C6500}"/>
+    <hyperlink ref="B30" r:id="rId6" xr:uid="{97BDF7E4-B0F2-4AD1-9E5D-B5401615F741}"/>
+    <hyperlink ref="B44" r:id="rId7" xr:uid="{B92225C7-A0E4-4217-AF3F-AADAF2D7499E}"/>
+    <hyperlink ref="B32" r:id="rId8" xr:uid="{9D2A5DB2-182C-4299-8BDF-7C7D44F45A57}"/>
+    <hyperlink ref="B33" r:id="rId9" xr:uid="{D047A243-352A-4994-B3A9-DF637941C7F3}"/>
+    <hyperlink ref="B34" r:id="rId10" xr:uid="{32BF2AA6-2E17-46BC-AA27-B8AC969413FE}"/>
+    <hyperlink ref="B35" r:id="rId11" xr:uid="{4BA1F5A2-68E7-473F-B487-10DCBA86929D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId12"/>
 </worksheet>
 </file>
--- a/backlink-building-data.xlsx
+++ b/backlink-building-data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Haider\Backlink-Building\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2984E2E-554A-44EA-8D55-ADC3914BC53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{995D6133-356A-461A-944C-DAB8A123D6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{C5600408-53AE-44CA-94F4-5B3C15A00001}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="69">
   <si>
     <t>Backlink Personal and resumebuilder.pk profile Data.</t>
   </si>
@@ -160,29 +160,95 @@
     <t>https://www.resumebuilder.pk/blog/how-to-write-professional-cover-letter-in-pakistan-2026</t>
   </si>
   <si>
-    <t>https://resumebuilder.pk/ai-resume-builder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request indexing on </t>
-  </si>
-  <si>
     <t>https://www.resumebuilder.pk/blog/ats-keywords-for-resumes</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t>https://resumebuilder.pk/cv-maker</t>
-  </si>
-  <si>
-    <t>https://www.resumebuilder.pk/</t>
+    <t>INDEXED</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/ai-resume-builder</t>
+  </si>
+  <si>
+    <t>INDEXED ALREADY</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/ats-resume-guide</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/bank-job-cv-format-in-pakistan-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/best-skills-for-a-resume-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/customer-service-representative-resume-example-2026</t>
+  </si>
+  <si>
+    <t>Not On Google</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/data-entry-operator-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/graphic-designer-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/how-to-write-a-cover-letter</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/how-to-write-a-professional-summary</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/how-to-write-achievements-on-a-resumettps://www.resumebuilder.pk/blog/how-to-write-achievements-on-a-resume</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/how-to-write-work-experience-on-a-resume</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/hr-manager-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/one-page-vs-two-page-resume</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/production-manager-resume-example-2026</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/resume-checklist-before-applying</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/resume-mistakes-to-avoid</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/cover-letter-builder</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/cv-maker</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/policies</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/resume-builder</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/reviews</t>
+  </si>
+  <si>
+    <t>NOT ON GOOGLE</t>
+  </si>
+  <si>
+    <t>REQUEST INDEXING</t>
+  </si>
+  <si>
+    <t>https://www.resumebuilder.pk/blog/textile-merchandiser-resume-example-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,17 +280,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Roboto"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -234,7 +289,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -257,14 +312,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -274,12 +402,28 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -609,72 +753,72 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="11"/>
-      <c r="B10" s="2" t="s">
+      <c r="A10" s="6"/>
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="6"/>
+      <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="11"/>
-      <c r="B12" s="2" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -699,256 +843,623 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50891E8-DCBC-4D2B-8051-6E7893B38F89}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A2:E54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" customWidth="1"/>
-    <col min="2" max="2" width="85.7109375" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="2" max="2" width="93.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" customWidth="1"/>
     <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="9.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="14">
+        <v>41</v>
+      </c>
+      <c r="D2" s="16"/>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="15">
+        <v>3</v>
+      </c>
+      <c r="D3" s="17"/>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C1">
+      <c r="C4" s="8">
+        <v>44</v>
+      </c>
+      <c r="D4" s="18"/>
+    </row>
+    <row r="5" spans="1:4" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>2</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>3</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>5</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>6</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>8</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>9</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>10</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>11</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>12</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>14</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>15</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>16</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>17</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>18</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>19</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>20</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>1</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>2</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>3</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>5</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="5"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>6</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>7</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="5"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>8</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="1"/>
+      <c r="E35" s="5"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>9</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="1"/>
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>10</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="1"/>
+      <c r="E37" s="5"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>11</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="5"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>12</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>13</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>14</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>15</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="5"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>16</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+      <c r="C43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="1"/>
+      <c r="E43" s="5"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>17</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D44" s="1"/>
+      <c r="E44" s="5"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>18</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D45" s="1"/>
+      <c r="E45" s="5"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
         <v>19</v>
       </c>
-      <c r="C2">
+      <c r="B46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="5"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5">
+      <c r="B47" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="5"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>21</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="5"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="5"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="B51" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D51" s="13">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="B52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D52" s="13">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>4</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>7</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>8</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>11</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>12</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>13</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>14</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>15</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>16</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>17</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>18</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>19</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>20</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="6"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>42</v>
-      </c>
-      <c r="E29" s="6">
-        <v>46201</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="6">
-        <v>46201</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="6">
-        <v>46201</v>
-      </c>
+      <c r="B53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D53" s="13">
+        <v>46204</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D2:D4"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B28" r:id="rId1" display="https://www.resumebuilder.pk/ai-resume-builder" xr:uid="{2A31CB2E-E9F6-43C8-9E3D-F82DCCBC06E7}"/>
+    <hyperlink ref="B32" r:id="rId1" xr:uid="{2A31CB2E-E9F6-43C8-9E3D-F82DCCBC06E7}"/>
     <hyperlink ref="B29" r:id="rId2" xr:uid="{12517903-CE33-4219-B72F-52864C17E0BE}"/>
-    <hyperlink ref="B31" r:id="rId3" xr:uid="{DCEC65B5-E9DA-4B67-BBAA-8AE2EDF8CCA2}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{CAEBC9F7-D231-40FE-827A-4CF63BFD1492}"/>
+    <hyperlink ref="B30" r:id="rId4" xr:uid="{ACD87C68-3669-4537-AB77-7A72908C6500}"/>
+    <hyperlink ref="B31" r:id="rId5" xr:uid="{97BDF7E4-B0F2-4AD1-9E5D-B5401615F741}"/>
+    <hyperlink ref="B51" r:id="rId6" xr:uid="{B92225C7-A0E4-4217-AF3F-AADAF2D7499E}"/>
+    <hyperlink ref="B33" r:id="rId7" xr:uid="{9D2A5DB2-182C-4299-8BDF-7C7D44F45A57}"/>
+    <hyperlink ref="B34" r:id="rId8" xr:uid="{D047A243-352A-4994-B3A9-DF637941C7F3}"/>
+    <hyperlink ref="B35" r:id="rId9" xr:uid="{32BF2AA6-2E17-46BC-AA27-B8AC969413FE}"/>
+    <hyperlink ref="B36" r:id="rId10" xr:uid="{4BA1F5A2-68E7-473F-B487-10DCBA86929D}"/>
+    <hyperlink ref="B37" r:id="rId11" xr:uid="{C968A6B1-105F-457A-9B2E-2F24E6776A87}"/>
+    <hyperlink ref="B38" r:id="rId12" xr:uid="{49C739FB-87C6-40A3-A15D-BF92FE3F6A14}"/>
+    <hyperlink ref="B39" r:id="rId13" xr:uid="{5FD3924A-1317-4164-B307-4753F57CF05F}"/>
+    <hyperlink ref="B40" r:id="rId14" xr:uid="{848D3FD2-B798-45E5-B871-BC0241CCE8C1}"/>
+    <hyperlink ref="B41" r:id="rId15" xr:uid="{2BC37E53-BD5D-4BD8-8B4C-DE4C6D91D451}"/>
+    <hyperlink ref="B42" r:id="rId16" xr:uid="{1272279C-BEAC-43B1-A72A-7C573AFB0B77}"/>
+    <hyperlink ref="B43" r:id="rId17" xr:uid="{852C65E1-C41E-479F-B235-48CA5E7BF2BA}"/>
+    <hyperlink ref="B44" r:id="rId18" xr:uid="{A3C9D3B6-1CCC-40DC-96AA-BB2C6EA83C3C}"/>
+    <hyperlink ref="B45" r:id="rId19" xr:uid="{F9E7D70A-E94F-4F5A-9BC3-68EE3BB14592}"/>
+    <hyperlink ref="B52" r:id="rId20" xr:uid="{80F79941-41E1-4B21-AE12-7B690A1C7C43}"/>
+    <hyperlink ref="B46" r:id="rId21" xr:uid="{3D339BB3-6AEF-46BC-BA0E-9B9A0FD1F352}"/>
+    <hyperlink ref="B53" r:id="rId22" xr:uid="{EAAEEC60-F175-4438-9FC9-8D29622C8A6C}"/>
+    <hyperlink ref="B47" r:id="rId23" xr:uid="{A721E78B-FCC8-45D8-9E1A-BC26569CF9BD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="256" orientation="portrait" horizontalDpi="203" verticalDpi="203" r:id="rId24"/>
 </worksheet>
 </file>